--- a/out/Attention-S4_repeat_5_000005.xlsx
+++ b/out/Attention-S4_repeat_5_000005.xlsx
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>7.999999562500022</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>7.999999562500022</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>7.999999562500022</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>0.04545455991735464</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>0.04545455991735464</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>7.999999562500022</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>0.04545455991735464</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>0.04545455991735464</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-S4_repeat_5_000005.xlsx
+++ b/out/Attention-S4_repeat_5_000005.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-S4_repeat_5_000005.xlsx
+++ b/out/Attention-S4_repeat_5_000005.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.01348956301808357</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.01157581806182861</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.51</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.009199157357215881</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.00922868400812149</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.00901525467634201</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.009886093437671661</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.009908691048622131</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.009538888931274414</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.01074288785457611</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.01067745685577393</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.01120010763406754</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.01107553392648697</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.01148911565542221</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.01133612543344498</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.01140653342008591</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.01178129762411118</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.01175207644701004</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.01408644765615463</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.01146440953016281</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.01552274823188782</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.01160623133182526</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.01155185699462891</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.01277963817119598</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.01386604085564613</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.01197145134210587</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.01306769624352455</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.01270921528339386</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.01177801936864853</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.01293032616376877</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.01420200988650322</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.01670638471841812</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.01190897077322006</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.01418235898017883</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.01430337503552437</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.01314504444599152</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.01262897998094559</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.01250793039798737</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.01158848404884338</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.01080805063247681</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.0106266662478447</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.01015704125165939</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.01109126210212708</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01102377474308014</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.01143991947174072</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.01212693005800247</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.01216679811477661</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.01236441731452942</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.01116134226322174</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.01037168502807617</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.009949959814548492</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.00986982136964798</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.009181521832942963</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.009496197104454041</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.01003562659025192</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.009329803287982941</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.01103224605321884</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.01008602231740952</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.01198561489582062</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.01177617907524109</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.0119139775633812</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.01215548068284988</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.01185343414545059</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.01186095923185349</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.01157246530056</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.01146342605352402</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.01164517551660538</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.01141415536403656</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.01129446923732758</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.01144109666347504</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57386,10 +57386,10 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.01108810305595398</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.01004821062088013</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.01103147119283676</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.01354330033063889</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.00849885493516922</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.01475254073739052</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.006154969334602356</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.007569774985313416</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.007373668253421783</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.009183555841445923</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.009667940437793732</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.01028727740049362</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.008827529847621918</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.004931770265102386</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.00796721875667572</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.007631614804267883</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.0115191712975502</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.0116892084479332</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.008011355996131897</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.007240064442157745</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.006312139332294464</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.006627462804317474</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.006211571395397186</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.007309019565582275</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.007044181227684021</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.008145466446876526</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.006248004734516144</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.007717721164226532</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.008769191801548004</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.009487397968769073</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.01000254601240158</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.01086015999317169</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.008640557527542114</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83617,14 +83617,14 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.009161882102489471</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84412,14 +84412,14 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.009750537574291229</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.008360885083675385</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.008085809648036957</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.01014687120914459</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.005533285439014435</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.007391259074211121</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.006725169718265533</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.008605964481830597</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.0155283585190773</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.01843306422233582</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.0150110237300396</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93157,14 +93157,14 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.02143281698226929</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.01244500279426575</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94747,14 +94747,14 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.01691503822803497</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.01080711930990219</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.01358503848314285</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97132,14 +97132,14 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.02027130126953125</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.01981128379702568</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.01732699573040009</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.01474571228027344</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.002374470233917236</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000024</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.02038683742284775</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1600000000000003</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>
